--- a/app/samples/certificate-template-3-sample.xlsx
+++ b/app/samples/certificate-template-3-sample.xlsx
@@ -414,7 +414,7 @@
         <v>Last Name</v>
       </c>
       <c r="C1" t="str">
-        <v>Course Line</v>
+        <v>Course</v>
       </c>
       <c r="D1" t="str">
         <v>Start Date</v>
@@ -425,13 +425,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ელიზავეტა</v>
+        <v>Elizaveta</v>
       </c>
       <c r="B2" t="str">
-        <v>დათუკიშვილს</v>
+        <v>Datukishvili</v>
       </c>
       <c r="C2" t="str">
-        <v>ხატვის კურსის წარმატებით დასრულებისთვის</v>
+        <v>General English</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -442,13 +442,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>გიორგი</v>
+        <v>GIORGI</v>
       </c>
       <c r="B3" t="str">
-        <v>ბერიძეს</v>
+        <v>BERIDZE</v>
       </c>
       <c r="C3" t="str">
-        <v>ინგლისური ენის კურსის წარმატებით დასრულებისთვის</v>
+        <v>General English</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-01</v>

--- a/app/samples/certificate-template-3-sample.xlsx
+++ b/app/samples/certificate-template-3-sample.xlsx
@@ -397,13 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,9 +418,12 @@
         <v>Course</v>
       </c>
       <c r="D1" t="str">
+        <v>Hours</v>
+      </c>
+      <c r="E1" t="str">
         <v>Start Date</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>End Date</v>
       </c>
     </row>
@@ -434,9 +438,12 @@
         <v>General English</v>
       </c>
       <c r="D2" t="str">
+        <v>48</v>
+      </c>
+      <c r="E2" t="str">
         <v>2026-01-16</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>2026-06-16</v>
       </c>
     </row>
@@ -450,16 +457,19 @@
       <c r="C3" t="str">
         <v>General English</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3">
+        <v>36</v>
+      </c>
+      <c r="E3" t="str">
         <v>2026-02-01</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>2026-07-01</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/app/samples/certificate-template-3-sample.xlsx
+++ b/app/samples/certificate-template-3-sample.xlsx
@@ -397,14 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,12 +417,9 @@
         <v>Course</v>
       </c>
       <c r="D1" t="str">
-        <v>Hours</v>
+        <v>Start Date</v>
       </c>
       <c r="E1" t="str">
-        <v>Start Date</v>
-      </c>
-      <c r="F1" t="str">
         <v>End Date</v>
       </c>
     </row>
@@ -438,12 +434,9 @@
         <v>General English</v>
       </c>
       <c r="D2" t="str">
-        <v>48</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="F2" t="str">
         <v>2026-06-16</v>
       </c>
     </row>
@@ -457,19 +450,16 @@
       <c r="C3" t="str">
         <v>General English</v>
       </c>
-      <c r="D3">
-        <v>36</v>
+      <c r="D3" t="str">
+        <v>2026-02-01</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="F3" t="str">
         <v>2026-07-01</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/app/samples/certificate-template-3-sample.xlsx
+++ b/app/samples/certificate-template-3-sample.xlsx
@@ -434,27 +434,27 @@
         <v>General English</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-16</v>
+        <v>16.01.2026</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-16</v>
+        <v>16.06.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GIORGI</v>
+        <v>Giorgi</v>
       </c>
       <c r="B3" t="str">
-        <v>BERIDZE</v>
+        <v>Beridze</v>
       </c>
       <c r="C3" t="str">
         <v>General English</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-01</v>
+        <v>01.02.2026</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-01</v>
+        <v>01.07.2026</v>
       </c>
     </row>
   </sheetData>
